--- a/DDモータ_コルモーゲン/Kollmorgen_DD_SVPWM_Calculator_v2_whitepaper_fixed_startup_accel_regen_JP_ldidt_regen_detailed_brake.xlsx
+++ b/DDモータ_コルモーゲン/Kollmorgen_DD_SVPWM_Calculator_v2_whitepaper_fixed_startup_accel_regen_JP_ldidt_regen_detailed_brake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9108h\Documents\GitHub\memo\DDモータ_コルモーゲン\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122EB564-8B31-4096-A18D-40762487C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AC9463-19B2-4805-98B5-168A8EA16C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10665" yWindow="135" windowWidth="17925" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -35,17 +35,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="460">
-  <si>
-    <t>Kollmorgen DDモータ / SVPWM 最低DCバス電圧 計算シート（白書整合版・日本語）</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="459">
   <si>
     <t>結果サマリー</t>
   </si>
   <si>
-    <t>※数式互換性のため、シート名は英語のままにしています。</t>
-  </si>
-  <si>
     <t>入力項目 / 設定</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
     <t>Vrms/krpm</t>
   </si>
   <si>
-    <t>本ブックで使用する線間RMSの Ke。上書きがあればそれを優先、なければ Kt/√2 から推定</t>
-  </si>
-  <si>
     <t>トルク T</t>
   </si>
   <si>
@@ -136,9 +127,6 @@
     <t>Vdc_min load (design)</t>
   </si>
   <si>
-    <t>入力したR倍率を用いた設計ケース</t>
-  </si>
-  <si>
     <t>Ke 上書き</t>
   </si>
   <si>
@@ -247,9 +235,6 @@
     <t>Vdc_min accel worst</t>
   </si>
   <si>
-    <t>起動電流を目標速度まで維持した加速ワースト。終速度での逆起電力を含む</t>
-  </si>
-  <si>
     <t>起動電流倍率</t>
   </si>
   <si>
@@ -466,12 +451,6 @@
     <t>必要抵抗値は『この値以下』を目安に選定し、許容パルスエネルギーも別途確認</t>
   </si>
   <si>
-    <t>起動過渡Vdc_min</t>
-  </si>
-  <si>
-    <t>起動時にLdi/dtを含めた大信号最低DCバス</t>
-  </si>
-  <si>
     <t>起動過渡Vdc+margin</t>
   </si>
   <si>
@@ -602,9 +581,6 @@
   </si>
   <si>
     <t>Kt から推定した線間 RMS の Ke</t>
-  </si>
-  <si>
-    <t>Ke_rms = Ke_crest / √2</t>
   </si>
   <si>
     <t>線間RMS逆起電力で使用</t>
@@ -1443,6 +1419,282 @@
     </r>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <r>
+      <t>Ke_rms = Ke_crest / √</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>入力した</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>倍率を用いた設計ケース</t>
+    </r>
+  </si>
+  <si>
+    <t>起動電流を目標速度まで維持した加速ワースト。
+終速度での逆起電力を含む</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>起動過渡</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>Vdc_min</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>起動時に</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ldi/dt</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>を含めた大信号最低</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>DC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>バス</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>本ブックで使用する線間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。上書きがあればそれを優先、なければ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Kt/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>√</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>から推定</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>Kollmorgen DD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>モータ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / SVPWM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>最低</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>バス電圧</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計算シート（白書整合版）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -1452,7 +1704,7 @@
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1495,6 +1747,63 @@
       <name val="Carlito"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1549,7 +1858,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1593,10 +1902,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1775,32 +2111,30 @@
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="29.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="85.35" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-    </row>
-    <row r="2" spans="1:10" ht="42.75">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1813,589 +2147,590 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" s="9">
         <f>Calculations!B6</f>
         <v>3.4047350620067647</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.25">
+      <c r="A5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.5">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="B5" s="5">
         <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="9">
         <f>Calculations!B12</f>
-        <v>656.80619435774497</v>
+        <v>536.28001202525036</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" s="5">
         <v>30.2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H6" s="9">
         <f>Calculations!B24</f>
-        <v>9.2886422791138195</v>
+        <v>7.5841446623571551</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5">
         <v>8.8699999999999992</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="9">
+      <c r="G7" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="18">
         <f>Calculations!B25</f>
-        <v>35.538041078825614</v>
+        <v>33.840879133152455</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H8" s="9">
         <f>Calculations!B27</f>
-        <v>39.091845186708177</v>
+        <v>37.224967046467704</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B9" s="5">
         <v>6.26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H9" s="9">
         <f>Calculations!B26</f>
-        <v>49.201976785961513</v>
+        <v>47.501249946033461</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5">
         <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H10" s="9">
         <f>Calculations!B28</f>
-        <v>54.122174464557666</v>
+        <v>52.251374940636808</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H11" s="10">
         <f>Calculations!B30</f>
-        <v>6.8094701240135294</v>
+        <v>6.3810597519729431</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
       <c r="A12" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5">
         <v>0.1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="10">
+      <c r="G12" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="19">
         <f>Calculations!B33</f>
-        <v>52.20754620661166</v>
+        <v>48.922965485003637</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H13" s="10">
         <f>Calculations!B34</f>
-        <v>57.428300827272828</v>
+        <v>53.815262033504006</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5">
       <c r="A14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="20">
+        <f>Calculations!B39</f>
+        <v>56.827241479610009</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="A15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="17">
+        <f>56.6/30.2</f>
+        <v>1.8741721854304636</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="11">
-        <f>Calculations!B39</f>
-        <v>61.831208841054703</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="8">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H15" s="11">
         <f>Calculations!B40</f>
-        <v>68.014329725160181</v>
+        <v>62.509965627571013</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.5">
       <c r="A16" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H16" s="1">
         <f>Calculations!B49</f>
         <v>1.6449340668482262</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1">
         <v>3</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H17" s="1">
         <f>Calculations!B44</f>
         <v>3.1415926535897931</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H18" s="1">
         <f>Calculations!B45</f>
         <v>0.35418180987483577</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1">
         <v>0.01</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H19" s="1">
         <f>Calculations!B48</f>
         <v>1.6449340668482262</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.5">
       <c r="A20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="16">
+        <v>93</v>
+      </c>
+      <c r="B20" s="15">
         <f>H14</f>
-        <v>61.831208841054703</v>
+        <v>56.827241479610009</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H20" s="1">
         <f>Calculations!B50</f>
         <v>1.1779262442499523</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="57">
       <c r="A21" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
         <f>Calculations!B53</f>
         <v>0.46700782259827389</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2406,158 +2741,158 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H22" s="1">
         <f>Calculations!B54</f>
-        <v>64.436675892815629</v>
+        <v>59.651673803436175</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="28.5">
       <c r="A23" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H23" s="1">
         <f>Calculations!B55</f>
-        <v>62.581945889096289</v>
+        <v>57.64318640309159</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.5">
       <c r="A24" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B24" s="1">
         <v>1000</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H24" s="1">
         <f>Calculations!B56</f>
-        <v>2.6054670517609253</v>
+        <v>2.8244323238261657</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="28.5">
       <c r="A25" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B25" s="1">
         <v>0.1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H25" s="1">
         <f>Calculations!B57</f>
-        <v>0.75073704804158581</v>
+        <v>0.81594492348158099</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H26" s="1" t="str">
         <f>Calculations!B58</f>
         <v>DCバス上昇あり</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="28.5">
       <c r="A27" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B27" s="1">
         <v>75</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -2567,95 +2902,95 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B28" s="1">
         <v>80</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H28" s="1">
         <f>Calculations!B60</f>
         <v>3.6741214057507987E-3</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="28.5">
       <c r="A29" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H29" s="1">
         <f>Calculations!B61</f>
         <v>43.317823641533252</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="28.5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="29.25">
       <c r="A30" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="G30" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="H30" s="21">
         <f>Calculations!B65</f>
-        <v>71.389232512555239</v>
+        <v>66.897856957129576</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>144</v>
+        <v>24</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2666,17 +3001,17 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H31" s="1">
         <f>Calculations!B66</f>
-        <v>78.528155763810773</v>
+        <v>73.587642652842547</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="28.5">
@@ -2687,152 +3022,152 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H32" s="1">
         <f>Calculations!B69</f>
-        <v>69.583460853321355</v>
+        <v>65.205693448642194</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="7:10">
       <c r="G33" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H33" s="8">
         <f>Calculations!B73</f>
         <v>2.1119418894465003</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="34" spans="7:10" ht="28.5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="7:10">
       <c r="G34" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H34" s="8">
         <f>Calculations!B74</f>
-        <v>9.0095080662693938</v>
+        <v>11.978323129090459</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="7:10" ht="28.5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="7:10">
       <c r="G35" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H35" s="8">
         <f>Calculations!B75</f>
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="7:10">
       <c r="G36" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H36" s="13" t="str">
         <f>Calculations!B76</f>
         <v>動作なし</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="7:10">
       <c r="G37" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H37" s="13" t="str">
         <f>Calculations!B77</f>
         <v>不要</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="7:10" ht="28.5">
       <c r="G38" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H38" s="8">
         <f>Calculations!B78</f>
         <v>2663.4255554608112</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="7:10">
       <c r="G39" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="H39" s="8">
         <f>Calculations!B79</f>
         <v>0.46700782259827389</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="7:10">
       <c r="G40" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="H40" s="8">
         <f>Calculations!B80</f>
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="7:10">
       <c r="G41" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H41" s="13" t="str">
         <f>Calculations!B81</f>
         <v>上限内</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2859,19 +3194,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -2880,782 +3213,782 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B4" s="4">
         <f>Inputs!B4*2*PI()/60</f>
         <v>1.0471975511965976</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B5" s="4">
         <f>B4*Inputs!B5</f>
         <v>33.510321638291124</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4">
         <f>Inputs!B6/Inputs!B7</f>
         <v>3.4047350620067647</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B7" s="4">
         <f>SQRT(2)*B6</f>
         <v>4.8150225009771681</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B8" s="4">
         <f>Inputs!B7</f>
         <v>8.8699999999999992</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
       <c r="A9" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B9" s="4">
-        <f>B8/SQRT(2)</f>
-        <v>6.2720371491246754</v>
+        <f>B8/SQRT(3)</f>
+        <v>5.12109688771198</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>189</v>
+        <v>452</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B10" s="4">
         <f>B9*1000*2*PI()/60</f>
-        <v>656.80619435774497</v>
+        <v>536.28001202525036</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B11" s="4">
         <f>IF(OR(Inputs!B8="",ISBLANK(Inputs!B8)),B9,Inputs!B8*60/(1000*2*PI()))</f>
-        <v>6.2720371491246754</v>
+        <v>5.12109688771198</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B12" s="4">
         <f>IF(OR(Inputs!B8="",ISBLANK(Inputs!B8)),B10,Inputs!B8)</f>
-        <v>656.80619435774497</v>
+        <v>536.28001202525036</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B13" s="4">
         <f>Inputs!B9/2*Inputs!B11</f>
         <v>3.13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B14" s="4">
         <f>Inputs!B9/2*1.525</f>
         <v>4.77325</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B15" s="4">
         <f>Inputs!B10/1000/2</f>
         <v>1.15E-2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B16" s="4">
         <f>B11*B4</f>
-        <v>6.5680619435774492</v>
+        <v>5.3628001202525031</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B17" s="4">
         <f>B16/SQRT(3)</f>
-        <v>3.7920723311785771</v>
+        <v>3.0962140930379403</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B18" s="4">
         <f>SQRT(2)*B17</f>
-        <v>5.3628001202525031</v>
+        <v>4.3787079623849676</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B19" s="4">
         <f>B13*B7</f>
         <v>15.071020428058535</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B20" s="4">
         <f>B14*B7</f>
         <v>22.983306152789268</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B21" s="4">
         <f>B5*B15*B7</f>
         <v>1.855558956088569</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B22" s="4">
         <f>SQRT(B21^2+(B18+B19)^2)</f>
-        <v>20.517897583331948</v>
+        <v>19.538040677139161</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B23" s="4">
         <f>SQRT(B21^2+(B18+B20)^2)</f>
-        <v>28.406774542036597</v>
+        <v>27.424859443186115</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B24" s="4">
         <f>SQRT(2)*B16</f>
-        <v>9.2886422791138195</v>
+        <v>7.5841446623571551</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B25" s="4">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" s="23">
         <f>SQRT(3)*B22</f>
-        <v>35.538041078825614</v>
+        <v>33.840879133152455</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B26" s="4">
         <f>SQRT(3)*B23</f>
-        <v>49.201976785961513</v>
+        <v>47.501249946033461</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B27" s="4">
         <f>B25*(1+Inputs!B12)</f>
-        <v>39.091845186708177</v>
+        <v>37.224967046467704</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B28" s="8">
         <f>B26*(1+Inputs!B12)</f>
-        <v>54.122174464557666</v>
+        <v>52.251374940636808</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B29" s="8">
         <f>Inputs!B15</f>
-        <v>2</v>
+        <v>1.8741721854304636</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B30" s="8">
         <f>B6*B29</f>
-        <v>6.8094701240135294</v>
+        <v>6.3810597519729431</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B31" s="8">
         <f>SQRT(2)*B30</f>
-        <v>9.6300450019543362</v>
+        <v>9.0241812435532349</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B32" s="8">
         <f>B13*B31</f>
-        <v>30.14204085611707</v>
+        <v>28.245687292321623</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="8">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="17">
         <f>SQRT(3)*B32</f>
-        <v>52.20754620661166</v>
+        <v>48.922965485003637</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B34" s="8">
         <f>B33*(1+Inputs!B12)</f>
-        <v>57.428300827272828</v>
+        <v>53.815262033504006</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B35" s="1">
         <f>B5*B15*B31</f>
-        <v>3.711117912177138</v>
+        <v>3.4776369839275829</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B36" s="1">
         <f>B18+B32</f>
-        <v>35.504840976369572</v>
+        <v>32.624395254706592</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B37" s="1">
         <f>SQRT(B35^2 + B36^2)</f>
-        <v>35.698265068702902</v>
+        <v>32.809223165556709</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B38" s="1">
         <f>SQRT(3/2)*B37</f>
-        <v>43.721267060471391</v>
+        <v>40.182927806357689</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" s="16">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="24">
         <f>SQRT(3)*B37</f>
-        <v>61.831208841054703</v>
+        <v>56.827241479610009</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B40" s="1">
         <f>B39*(1+Inputs!$B$12)</f>
-        <v>68.014329725160181</v>
+        <v>62.509965627571013</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3665,356 +3998,356 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B42" s="1">
         <f>B4</f>
         <v>1.0471975511965976</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B43" s="1">
         <f>B42/Inputs!B18</f>
         <v>1.0471975511965976</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B44" s="1">
         <f>Inputs!B17*B43</f>
         <v>3.1415926535897931</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B45" s="1">
         <f>B44/Inputs!B7</f>
         <v>0.35418180987483577</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B46" s="1">
         <f>SQRT(2)*B45</f>
         <v>0.50088871907084176</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B47" s="1">
         <f>B44*B42</f>
         <v>3.2898681336964524</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B48" s="1">
         <f>0.5*B44*B42</f>
         <v>1.6449340668482262</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B49" s="1">
         <f>0.5*Inputs!B17*B42^2</f>
         <v>1.6449340668482262</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B50" s="1">
         <f>3*B45^2*B13</f>
         <v>1.1779262442499523</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B51" s="1">
         <f>B50*Inputs!B18</f>
         <v>1.1779262442499523</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B52" s="1">
         <f>B48-B50</f>
         <v>0.46700782259827389</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B53" s="1">
         <f>MAX(B49-B51,0)</f>
         <v>0.46700782259827389</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B54" s="1">
         <f>IF(Inputs!B19&gt;0,SQRT(Inputs!B20^2+2*B49/Inputs!B19),NA())</f>
-        <v>64.436675892815629</v>
+        <v>59.651673803436175</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B55" s="1">
         <f>IF(Inputs!B19&gt;0,SQRT(Inputs!B20^2+2*B53/Inputs!B19),NA())</f>
-        <v>62.581945889096289</v>
+        <v>57.64318640309159</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B56" s="1">
         <f>B54-Inputs!B20</f>
-        <v>2.6054670517609253</v>
+        <v>2.8244323238261657</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B57" s="1">
         <f>B55-Inputs!B20</f>
-        <v>0.75073704804158581</v>
+        <v>0.81594492348158099</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B58" s="1" t="str">
         <f>IF(B52&gt;0,"DCバス上昇あり","銅損が上回るためDCバス上昇なし")</f>
         <v>DCバス上昇あり</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F58" s="1"/>
     </row>
@@ -4028,463 +4361,463 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B60" s="1">
         <f>IF(Inputs!B9&gt;0,(Inputs!B10/1000)/Inputs!B9,NA())</f>
         <v>3.6741214057507987E-3</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B61" s="1">
         <f>IF(ISNUMBER(B60),1/(2*PI()*B60),NA())</f>
         <v>43.317823641533252</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B62" s="1">
         <f>Inputs!B23/1000</f>
         <v>0.01</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B63" s="1">
         <f>B15*B31/B62</f>
-        <v>11.074551752247487</v>
+        <v>10.377808430086221</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B64" s="1">
         <f>B32+B63</f>
-        <v>41.216592608364557</v>
+        <v>38.623495722407846</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B65" s="1">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15">
+      <c r="A65" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B65" s="21">
         <f>SQRT(3)*B64</f>
-        <v>71.389232512555239</v>
+        <v>66.897856957129576</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B66" s="1">
         <f>B65*(1+Inputs!B12)</f>
-        <v>78.528155763810773</v>
+        <v>73.587642652842547</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B67" s="1">
         <f>Inputs!B24</f>
         <v>1000</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B68" s="1">
         <f>B31*Inputs!B25</f>
-        <v>0.96300450019543371</v>
+        <v>0.90241812435532354</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B69" s="1">
         <f>B15*2*PI()*B67*B68</f>
-        <v>69.583460853321355</v>
+        <v>65.205693448642194</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="27.75">
       <c r="A70" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B71" s="12">
         <f>Inputs!B27</f>
         <v>75</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B72" s="12">
         <f>Inputs!B28</f>
         <v>80</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B73" s="8">
         <f>MAX(B47-B50,0)</f>
         <v>2.1119418894465003</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B74" s="8">
         <f>MAX(0,0.5*Inputs!B19*(B71^2-Inputs!B20^2))</f>
-        <v>9.0095080662693938</v>
+        <v>11.978323129090459</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B75" s="8">
         <f>MAX(B53-B74,0)</f>
         <v>0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B76" s="8" t="str">
         <f>IF(B53&lt;=0,"動作なし",IF(B55&gt;=B71,"動作見込みあり","動作なし"))</f>
         <v>動作なし</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B77" s="8" t="str">
         <f>IF(B53&lt;=0,"不要",IF(B55&gt;=B71,"必要","不要"))</f>
         <v>不要</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B78" s="8">
         <f>IF(B73&gt;0,B71^2/B73,NA())</f>
         <v>2663.4255554608112</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B79" s="8">
         <f>MAX(B52,0)</f>
         <v>0.46700782259827389</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B80" s="8">
         <f>B75</f>
         <v>0</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B81" s="1" t="str">
         <f>IF(B55&gt;B72,"上限超過",IF(B55&gt;=B71,"チョッパ領域内","上限内"))</f>
         <v>上限内</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4515,335 +4848,333 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="B1" s="15"/>
-    </row>
-    <row r="2" spans="1:2" ht="68.45" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A1" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.100000000000001" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.5">
+      <c r="A6" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="68.45" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="9" spans="1:2" ht="28.5">
+      <c r="A9" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="51.2" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="10" spans="1:2" ht="28.5">
+      <c r="A10" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="11" spans="1:2" ht="28.5">
+      <c r="A11" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A9" s="1" t="s">
+    <row r="13" spans="1:2" ht="28.5">
+      <c r="A13" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A10" s="1" t="s">
+    <row r="14" spans="1:2" ht="28.5">
+      <c r="A14" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A11" s="1" t="s">
+    <row r="15" spans="1:2" ht="28.5">
+      <c r="A15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="28.5">
+      <c r="A16" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="28.5">
+      <c r="A17" s="1" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="28.5">
+      <c r="A18" s="1" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="51.2" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="28.5">
+      <c r="A19" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="51.2" customHeight="1">
-      <c r="A16" s="1" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A17" s="1" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A18" s="1" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="28.5">
+      <c r="A24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="51.2" customHeight="1">
-      <c r="A19" s="1" t="s">
+    <row r="25" spans="1:2" ht="28.5">
+      <c r="A25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="28.5">
+      <c r="A26" s="1" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="28.5">
+      <c r="A27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="28" spans="1:2" ht="28.5">
+      <c r="A28" s="1" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17.100000000000001" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="1" t="s">
+    <row r="29" spans="1:2" ht="42.75">
+      <c r="A29" s="1" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="51.2" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="1" t="s">
+    <row r="30" spans="1:2" ht="28.5">
+      <c r="A30" s="1" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A26" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="28.5">
+      <c r="A31" s="1" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A28" s="1" t="s">
+    <row r="32" spans="1:2" ht="28.5">
+      <c r="A32" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="68.45" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="33" spans="1:2" ht="42.75">
+      <c r="A33" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A30" s="1" t="s">
+    <row r="34" spans="1:2" ht="28.5">
+      <c r="A34" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A31" s="1" t="s">
+    <row r="35" spans="1:2" ht="28.5">
+      <c r="A35" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>441</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="51.2" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="68.45" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="68.45" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="28.5">
       <c r="A36" s="1" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="28.5">
       <c r="A37" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="28.5">
       <c r="A38" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="28.5">
       <c r="A40" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="42.75">
       <c r="A41" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="28.5">
       <c r="A42" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
